--- a/challenge 2026 12_2.xlsx
+++ b/challenge 2026 12_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjakob\Downloads\feltölteni\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjakob\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E13FED7-ABAE-4BFC-99C0-94BADB08A746}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4407B2DB-A307-4D1C-8A63-B6BEDB0241DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1464,7 +1464,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008E6A3848}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1542,7 +1542,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000E7A3634F}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1579,7 +1579,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000FF44816C}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2001,7 +2001,9 @@
       <c r="K5" s="9">
         <v>114</v>
       </c>
-      <c r="L5" s="9"/>
+      <c r="L5" s="9">
+        <v>113.9</v>
+      </c>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -2013,11 +2015,11 @@
         <v>112</v>
       </c>
       <c r="U5" s="10">
-        <f>C5-T5</f>
+        <f t="shared" ref="U5:U17" si="0">C5-T5</f>
         <v>4.0999999999999943</v>
       </c>
       <c r="V5" s="11">
-        <f>U5/C5</f>
+        <f t="shared" ref="V5:V17" si="1">U5/C5</f>
         <v>3.5314384151593409E-2</v>
       </c>
       <c r="W5" s="10" t="e">
@@ -2025,7 +2027,7 @@
         <v>#REF!</v>
       </c>
       <c r="X5" s="12" t="e">
-        <f t="shared" ref="X5:X19" si="0">RANK(W5,$W$5:$W$19,0)</f>
+        <f t="shared" ref="X5:X19" si="2">RANK(W5,$W$5:$W$19,0)</f>
         <v>#REF!</v>
       </c>
       <c r="Y5" s="11" t="e">
@@ -2033,7 +2035,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z5" s="12" t="e">
-        <f t="shared" ref="Z5:Z19" si="1">RANK(Y5,$Y$5:$Y$19,0)</f>
+        <f t="shared" ref="Z5:Z19" si="3">RANK(Y5,$Y$5:$Y$19,0)</f>
         <v>#REF!</v>
       </c>
     </row>
@@ -2068,7 +2070,9 @@
       <c r="K6" s="9">
         <v>101.8</v>
       </c>
-      <c r="L6" s="9"/>
+      <c r="L6" s="9">
+        <v>100.6</v>
+      </c>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
@@ -2080,11 +2084,11 @@
         <v>98</v>
       </c>
       <c r="U6" s="13">
-        <f>C6-T6</f>
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="V6" s="11">
-        <f>U6/C6</f>
+        <f t="shared" si="1"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="W6" s="13" t="e">
@@ -2092,7 +2096,7 @@
         <v>#REF!</v>
       </c>
       <c r="X6" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y6" s="11" t="e">
@@ -2100,7 +2104,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z6" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2135,7 +2139,9 @@
       <c r="K7" s="9">
         <v>111.8</v>
       </c>
-      <c r="L7" s="9"/>
+      <c r="L7" s="9">
+        <v>112</v>
+      </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
@@ -2147,11 +2153,11 @@
         <v>113</v>
       </c>
       <c r="U7" s="13">
-        <f>C7-T7</f>
+        <f t="shared" si="0"/>
         <v>3.2999999999999972</v>
       </c>
       <c r="V7" s="11">
-        <f>U7/C7</f>
+        <f t="shared" si="1"/>
         <v>2.8374892519346495E-2</v>
       </c>
       <c r="W7" s="13" t="e">
@@ -2159,7 +2165,7 @@
         <v>#REF!</v>
       </c>
       <c r="X7" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y7" s="11" t="e">
@@ -2167,7 +2173,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z7" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2202,7 +2208,9 @@
       <c r="K8" s="9">
         <v>87.7</v>
       </c>
-      <c r="L8" s="9"/>
+      <c r="L8" s="9">
+        <v>87.6</v>
+      </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
@@ -2214,11 +2222,11 @@
         <v>85</v>
       </c>
       <c r="U8" s="13">
-        <f>C8-T8</f>
+        <f t="shared" si="0"/>
         <v>2.7000000000000028</v>
       </c>
       <c r="V8" s="11">
-        <f>U8/C8</f>
+        <f t="shared" si="1"/>
         <v>3.078677309007985E-2</v>
       </c>
       <c r="W8" s="13" t="e">
@@ -2226,7 +2234,7 @@
         <v>#REF!</v>
       </c>
       <c r="X8" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y8" s="11" t="e">
@@ -2234,7 +2242,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z8" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2269,7 +2277,9 @@
       <c r="K9" s="9">
         <v>83.4</v>
       </c>
-      <c r="L9" s="9"/>
+      <c r="L9" s="9">
+        <v>82.9</v>
+      </c>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
@@ -2281,11 +2291,11 @@
         <v>80</v>
       </c>
       <c r="U9" s="13">
-        <f>C9-T9</f>
+        <f t="shared" si="0"/>
         <v>8.2999999999999972</v>
       </c>
       <c r="V9" s="11">
-        <f>U9/C9</f>
+        <f t="shared" si="1"/>
         <v>9.3997734994337459E-2</v>
       </c>
       <c r="W9" s="13" t="e">
@@ -2293,7 +2303,7 @@
         <v>#REF!</v>
       </c>
       <c r="X9" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y9" s="11" t="e">
@@ -2301,7 +2311,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z9" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2336,7 +2346,9 @@
       <c r="K10" s="9">
         <v>101.6</v>
       </c>
-      <c r="L10" s="9"/>
+      <c r="L10" s="9">
+        <v>101.4</v>
+      </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
@@ -2348,11 +2360,11 @@
         <v>95</v>
       </c>
       <c r="U10" s="13">
-        <f>C10-T10</f>
+        <f t="shared" si="0"/>
         <v>10.299999999999997</v>
       </c>
       <c r="V10" s="11">
-        <f>U10/C10</f>
+        <f t="shared" si="1"/>
         <v>9.7815764482431122E-2</v>
       </c>
       <c r="W10" s="13" t="e">
@@ -2360,7 +2372,7 @@
         <v>#REF!</v>
       </c>
       <c r="X10" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y10" s="11" t="e">
@@ -2368,7 +2380,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z10" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2403,7 +2415,9 @@
       <c r="K11" s="9">
         <v>92</v>
       </c>
-      <c r="L11" s="9"/>
+      <c r="L11" s="9">
+        <v>92.8</v>
+      </c>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
@@ -2415,11 +2429,11 @@
         <v>89</v>
       </c>
       <c r="U11" s="13">
-        <f>C11-T11</f>
+        <f t="shared" si="0"/>
         <v>3.2999999999999972</v>
       </c>
       <c r="V11" s="11">
-        <f>U11/C11</f>
+        <f t="shared" si="1"/>
         <v>3.5752979414951216E-2</v>
       </c>
       <c r="W11" s="13" t="e">
@@ -2427,7 +2441,7 @@
         <v>#REF!</v>
       </c>
       <c r="X11" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y11" s="11" t="e">
@@ -2435,7 +2449,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z11" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2470,7 +2484,9 @@
       <c r="K12" s="9">
         <v>102.3</v>
       </c>
-      <c r="L12" s="9"/>
+      <c r="L12" s="9">
+        <v>101.5</v>
+      </c>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
@@ -2482,11 +2498,11 @@
         <v>100</v>
       </c>
       <c r="U12" s="13">
-        <f>C12-T12</f>
+        <f t="shared" si="0"/>
         <v>8.4000000000000057</v>
       </c>
       <c r="V12" s="11">
-        <f>U12/C12</f>
+        <f t="shared" si="1"/>
         <v>7.7490774907749124E-2</v>
       </c>
       <c r="W12" s="13" t="e">
@@ -2494,7 +2510,7 @@
         <v>#REF!</v>
       </c>
       <c r="X12" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y12" s="11" t="e">
@@ -2502,7 +2518,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z12" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2537,7 +2553,9 @@
       <c r="K13" s="9">
         <v>99.2</v>
       </c>
-      <c r="L13" s="9"/>
+      <c r="L13" s="9">
+        <v>98.8</v>
+      </c>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
@@ -2549,11 +2567,11 @@
         <v>95</v>
       </c>
       <c r="U13" s="13">
-        <f>C13-T13</f>
+        <f t="shared" si="0"/>
         <v>7.0999999999999943</v>
       </c>
       <c r="V13" s="11">
-        <f>U13/C13</f>
+        <f t="shared" si="1"/>
         <v>6.9539666993143928E-2</v>
       </c>
       <c r="W13" s="13" t="e">
@@ -2561,7 +2579,7 @@
         <v>#REF!</v>
       </c>
       <c r="X13" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y13" s="11" t="e">
@@ -2569,7 +2587,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z13" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2604,7 +2622,9 @@
       <c r="K14" s="9">
         <v>96.7</v>
       </c>
-      <c r="L14" s="9"/>
+      <c r="L14" s="9">
+        <v>94.9</v>
+      </c>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
@@ -2616,11 +2636,11 @@
         <v>95.9</v>
       </c>
       <c r="U14" s="13">
-        <f>C14-T14</f>
+        <f t="shared" si="0"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="V14" s="11">
-        <f>U14/C14</f>
+        <f t="shared" si="1"/>
         <v>1.3374485596707789E-2</v>
       </c>
       <c r="W14" s="13" t="e">
@@ -2628,7 +2648,7 @@
         <v>#REF!</v>
       </c>
       <c r="X14" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y14" s="11" t="e">
@@ -2636,7 +2656,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z14" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2671,7 +2691,9 @@
       <c r="K15" s="9">
         <v>73.900000000000006</v>
       </c>
-      <c r="L15" s="9"/>
+      <c r="L15" s="9">
+        <v>73.099999999999994</v>
+      </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
@@ -2683,11 +2705,11 @@
         <v>72</v>
       </c>
       <c r="U15" s="13">
-        <f>C15-T15</f>
+        <f t="shared" si="0"/>
         <v>8.0999999999999943</v>
       </c>
       <c r="V15" s="11">
-        <f>U15/C15</f>
+        <f t="shared" si="1"/>
         <v>0.10112359550561792</v>
       </c>
       <c r="W15" s="13" t="e">
@@ -2695,7 +2717,7 @@
         <v>#REF!</v>
       </c>
       <c r="X15" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y15" s="11" t="e">
@@ -2703,7 +2725,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z15" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2738,7 +2760,9 @@
       <c r="K16" s="9">
         <v>62</v>
       </c>
-      <c r="L16" s="9"/>
+      <c r="L16" s="9">
+        <v>62</v>
+      </c>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
@@ -2750,11 +2774,11 @@
         <v>55</v>
       </c>
       <c r="U16" s="13">
-        <f>C16-T16</f>
+        <f t="shared" si="0"/>
         <v>8.1000000000000014</v>
       </c>
       <c r="V16" s="11">
-        <f>U16/C16</f>
+        <f t="shared" si="1"/>
         <v>0.12836767036450081</v>
       </c>
       <c r="W16" s="13" t="e">
@@ -2762,7 +2786,7 @@
         <v>#REF!</v>
       </c>
       <c r="X16" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y16" s="11" t="e">
@@ -2770,7 +2794,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z16" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2805,7 +2829,9 @@
       <c r="K17" s="9">
         <v>70.099999999999994</v>
       </c>
-      <c r="L17" s="9"/>
+      <c r="L17" s="9">
+        <v>70</v>
+      </c>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
@@ -2817,11 +2843,11 @@
         <v>72</v>
       </c>
       <c r="U17" s="13">
-        <f>C17-T17</f>
+        <f t="shared" si="0"/>
         <v>-3.4000000000000057</v>
       </c>
       <c r="V17" s="11">
-        <f>U17/C17</f>
+        <f t="shared" si="1"/>
         <v>-4.9562682215743524E-2</v>
       </c>
       <c r="W17" s="13" t="e">
@@ -2829,7 +2855,7 @@
         <v>#REF!</v>
       </c>
       <c r="X17" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y17" s="11" t="e">
@@ -2837,7 +2863,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z17" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2872,7 +2898,9 @@
       <c r="K18" s="9">
         <v>102.6</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="9">
+        <v>101.6</v>
+      </c>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
@@ -2896,7 +2924,7 @@
         <v>#REF!</v>
       </c>
       <c r="X18" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y18" s="11" t="e">
@@ -2904,7 +2932,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z18" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -2939,7 +2967,9 @@
       <c r="K19" s="9">
         <v>92.8</v>
       </c>
-      <c r="L19" s="9"/>
+      <c r="L19" s="9">
+        <v>92.5</v>
+      </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
@@ -2963,7 +2993,7 @@
         <v>#REF!</v>
       </c>
       <c r="X19" s="12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="Y19" s="11" t="e">
@@ -2971,7 +3001,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z19" s="12" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -3138,7 +3168,7 @@
       </c>
       <c r="L5" s="14">
         <f>'2026 tavasz'!L5</f>
-        <v>0</v>
+        <v>113.9</v>
       </c>
       <c r="M5" s="14">
         <f>'2026 tavasz'!M5</f>
@@ -3212,7 +3242,7 @@
       </c>
       <c r="L6" s="14">
         <f>'2026 tavasz'!L6</f>
-        <v>0</v>
+        <v>100.6</v>
       </c>
       <c r="M6" s="14">
         <f>'2026 tavasz'!M6</f>
@@ -3286,7 +3316,7 @@
       </c>
       <c r="L7" s="14">
         <f>'2026 tavasz'!L7</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M7" s="14">
         <f>'2026 tavasz'!M7</f>
@@ -3360,7 +3390,7 @@
       </c>
       <c r="L8" s="14">
         <f>'2026 tavasz'!L8</f>
-        <v>0</v>
+        <v>87.6</v>
       </c>
       <c r="M8" s="14">
         <f>'2026 tavasz'!M8</f>
@@ -3434,7 +3464,7 @@
       </c>
       <c r="L9" s="14">
         <f>'2026 tavasz'!L9</f>
-        <v>0</v>
+        <v>82.9</v>
       </c>
       <c r="M9" s="14">
         <f>'2026 tavasz'!M9</f>
@@ -3507,8 +3537,8 @@
         <v>101.6</v>
       </c>
       <c r="L10" s="14">
-        <f>'2026 tavasz'!L10</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L11</f>
+        <v>92.8</v>
       </c>
       <c r="M10" s="14">
         <f>'2026 tavasz'!M10</f>
@@ -3581,8 +3611,8 @@
         <v>92</v>
       </c>
       <c r="L11" s="14">
-        <f>'2026 tavasz'!L11</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L12</f>
+        <v>101.5</v>
       </c>
       <c r="M11" s="14">
         <f>'2026 tavasz'!M11</f>
@@ -3655,8 +3685,8 @@
         <v>102.3</v>
       </c>
       <c r="L12" s="14">
-        <f>'2026 tavasz'!L12</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L13</f>
+        <v>98.8</v>
       </c>
       <c r="M12" s="14">
         <f>'2026 tavasz'!M12</f>
@@ -3729,8 +3759,8 @@
         <v>99.2</v>
       </c>
       <c r="L13" s="14">
-        <f>'2026 tavasz'!L13</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L14</f>
+        <v>94.9</v>
       </c>
       <c r="M13" s="14">
         <f>'2026 tavasz'!M13</f>
@@ -3803,8 +3833,8 @@
         <v>96.7</v>
       </c>
       <c r="L14" s="14">
-        <f>'2026 tavasz'!L14</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L15</f>
+        <v>73.099999999999994</v>
       </c>
       <c r="M14" s="14">
         <f>'2026 tavasz'!M14</f>
@@ -3873,8 +3903,8 @@
         <v>73.900000000000006</v>
       </c>
       <c r="L15" s="14">
-        <f>'2026 tavasz'!L15</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L16</f>
+        <v>62</v>
       </c>
       <c r="M15" s="14">
         <f>'2026 tavasz'!M15</f>
@@ -3943,8 +3973,8 @@
         <v>62</v>
       </c>
       <c r="L16" s="14">
-        <f>'2026 tavasz'!L16</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L17</f>
+        <v>70</v>
       </c>
       <c r="M16" s="14">
         <f>'2026 tavasz'!M16</f>
@@ -4013,8 +4043,8 @@
         <v>70.099999999999994</v>
       </c>
       <c r="L17" s="14">
-        <f>'2026 tavasz'!L17</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L18</f>
+        <v>101.6</v>
       </c>
       <c r="M17" s="14">
         <f>'2026 tavasz'!M17</f>
@@ -4225,7 +4255,7 @@
       </c>
       <c r="L22" s="11">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-1.8949181739879317E-2</v>
       </c>
       <c r="M22" s="11">
         <f t="shared" si="2"/>
@@ -4294,7 +4324,7 @@
       </c>
       <c r="L23" s="11">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-8.8669950738916817E-3</v>
       </c>
       <c r="M23" s="11">
         <f t="shared" si="3"/>
@@ -4363,7 +4393,7 @@
       </c>
       <c r="L24" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-3.6973344797936347E-2</v>
       </c>
       <c r="M24" s="11">
         <f t="shared" si="4"/>
@@ -4432,7 +4462,7 @@
       </c>
       <c r="L25" s="11">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>-1.1402508551882386E-3</v>
       </c>
       <c r="M25" s="11">
         <f t="shared" si="5"/>
@@ -4501,7 +4531,7 @@
       </c>
       <c r="L26" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-6.1155152887882126E-2</v>
       </c>
       <c r="M26" s="11">
         <f t="shared" si="6"/>
@@ -4570,7 +4600,7 @@
       </c>
       <c r="L27" s="11">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>-0.11870845204178537</v>
       </c>
       <c r="M27" s="11">
         <f t="shared" si="7"/>
@@ -4639,7 +4669,7 @@
       </c>
       <c r="L28" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>9.9674972914409563E-2</v>
       </c>
       <c r="M28" s="11">
         <f t="shared" si="8"/>
@@ -4708,7 +4738,7 @@
       </c>
       <c r="L29" s="11">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>-8.8560885608856166E-2</v>
       </c>
       <c r="M29" s="11">
         <f t="shared" si="9"/>
@@ -4778,7 +4808,7 @@
       </c>
       <c r="L30" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-7.0519098922624771E-2</v>
       </c>
       <c r="M30" s="11">
         <f t="shared" si="10"/>
@@ -4846,7 +4876,7 @@
       </c>
       <c r="L31" s="11">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>-0.24794238683127581</v>
       </c>
       <c r="M31" s="11">
         <f t="shared" si="11"/>
@@ -4914,7 +4944,7 @@
       </c>
       <c r="L32" s="11">
         <f t="shared" si="12"/>
-        <v>-1</v>
+        <v>-0.22596754057428209</v>
       </c>
       <c r="M32" s="11">
         <f t="shared" si="12"/>
@@ -4982,7 +5012,7 @@
       </c>
       <c r="L33" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.10935023771790806</v>
       </c>
       <c r="M33" s="11">
         <f t="shared" si="13"/>
@@ -5050,7 +5080,7 @@
       </c>
       <c r="L34" s="11">
         <f t="shared" si="14"/>
-        <v>-1</v>
+        <v>0.48104956268221577</v>
       </c>
       <c r="M34" s="11">
         <f t="shared" si="14"/>
@@ -8031,7 +8061,7 @@
       </c>
       <c r="AN5" s="9">
         <f>'2026 tavasz'!L5</f>
-        <v>0</v>
+        <v>113.9</v>
       </c>
       <c r="AO5" s="9">
         <f>'2026 tavasz'!M5</f>
@@ -8178,7 +8208,7 @@
       </c>
       <c r="AN6" s="9">
         <f>'2026 tavasz'!L6</f>
-        <v>0</v>
+        <v>100.6</v>
       </c>
       <c r="AO6" s="9">
         <f>'2026 tavasz'!M6</f>
@@ -8325,7 +8355,7 @@
       </c>
       <c r="AN7" s="9">
         <f>'2026 tavasz'!L7</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AO7" s="9">
         <f>'2026 tavasz'!M7</f>
@@ -8472,7 +8502,7 @@
       </c>
       <c r="AN8" s="9">
         <f>'2026 tavasz'!L8</f>
-        <v>0</v>
+        <v>87.6</v>
       </c>
       <c r="AO8" s="9">
         <f>'2026 tavasz'!M8</f>
@@ -8619,7 +8649,7 @@
       </c>
       <c r="AN9" s="9">
         <f>'2026 tavasz'!L9</f>
-        <v>0</v>
+        <v>82.9</v>
       </c>
       <c r="AO9" s="9">
         <f>'2026 tavasz'!M9</f>
@@ -8765,8 +8795,8 @@
         <v>101.6</v>
       </c>
       <c r="AN10" s="9">
-        <f>'2026 tavasz'!L10</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L11</f>
+        <v>92.8</v>
       </c>
       <c r="AO10" s="9">
         <f>'2026 tavasz'!M10</f>
@@ -8912,8 +8942,8 @@
         <v>92</v>
       </c>
       <c r="AN11" s="9">
-        <f>'2026 tavasz'!L11</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L12</f>
+        <v>101.5</v>
       </c>
       <c r="AO11" s="9">
         <f>'2026 tavasz'!M11</f>
@@ -9059,8 +9089,8 @@
         <v>102.3</v>
       </c>
       <c r="AN12" s="9">
-        <f>'2026 tavasz'!L12</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L13</f>
+        <v>98.8</v>
       </c>
       <c r="AO12" s="9">
         <f>'2026 tavasz'!M12</f>
@@ -9206,8 +9236,8 @@
         <v>99.2</v>
       </c>
       <c r="AN13" s="9">
-        <f>'2026 tavasz'!L13</f>
-        <v>0</v>
+        <f>'2026 tavasz'!L14</f>
+        <v>94.9</v>
       </c>
       <c r="AO13" s="9">
         <f>'2026 tavasz'!M13</f>
@@ -9630,9 +9660,9 @@
         <f>LEFT('Éves adatsor'!AM5, LEN('Éves adatsor'!AM5) - 3)</f>
         <v/>
       </c>
-      <c r="AN5" s="14" t="e">
+      <c r="AN5" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN5, LEN('Éves adatsor'!AN5) - 3)</f>
-        <v>#VALUE!</v>
+        <v>11</v>
       </c>
       <c r="AO5" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO5, LEN('Éves adatsor'!AO5) - 3)</f>
@@ -9807,9 +9837,9 @@
         <f>LEFT('Éves adatsor'!AM6, LEN('Éves adatsor'!AM6) - 3)</f>
         <v>10</v>
       </c>
-      <c r="AN6" s="14" t="e">
+      <c r="AN6" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN6, LEN('Éves adatsor'!AN6) - 3)</f>
-        <v>#VALUE!</v>
+        <v>10</v>
       </c>
       <c r="AO6" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO6, LEN('Éves adatsor'!AO6) - 3)</f>
@@ -9984,9 +10014,9 @@
         <f>LEFT('Éves adatsor'!AM7, LEN('Éves adatsor'!AM7) - 3)</f>
         <v>11</v>
       </c>
-      <c r="AN7" s="14" t="e">
+      <c r="AN7" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN7, LEN('Éves adatsor'!AN7) - 3)</f>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="AO7" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO7, LEN('Éves adatsor'!AO7) - 3)</f>
@@ -10161,9 +10191,9 @@
         <f>LEFT('Éves adatsor'!AM8, LEN('Éves adatsor'!AM8) - 3)</f>
         <v>8</v>
       </c>
-      <c r="AN8" s="14" t="e">
+      <c r="AN8" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN8, LEN('Éves adatsor'!AN8) - 3)</f>
-        <v>#VALUE!</v>
+        <v>8</v>
       </c>
       <c r="AO8" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO8, LEN('Éves adatsor'!AO8) - 3)</f>
@@ -10338,9 +10368,9 @@
         <f>LEFT('Éves adatsor'!AM9, LEN('Éves adatsor'!AM9) - 3)</f>
         <v>8</v>
       </c>
-      <c r="AN9" s="14" t="e">
+      <c r="AN9" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN9, LEN('Éves adatsor'!AN9) - 3)</f>
-        <v>#VALUE!</v>
+        <v>8</v>
       </c>
       <c r="AO9" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO9, LEN('Éves adatsor'!AO9) - 3)</f>
@@ -10515,9 +10545,9 @@
         <f>LEFT('Éves adatsor'!AM10, LEN('Éves adatsor'!AM10) - 3)</f>
         <v>10</v>
       </c>
-      <c r="AN10" s="14" t="e">
+      <c r="AN10" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN10, LEN('Éves adatsor'!AN10) - 3)</f>
-        <v>#VALUE!</v>
+        <v>9</v>
       </c>
       <c r="AO10" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO10, LEN('Éves adatsor'!AO10) - 3)</f>
@@ -10692,9 +10722,9 @@
         <f>LEFT('Éves adatsor'!AM11, LEN('Éves adatsor'!AM11) - 3)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AN11" s="14" t="e">
+      <c r="AN11" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN11, LEN('Éves adatsor'!AN11) - 3)</f>
-        <v>#VALUE!</v>
+        <v>10</v>
       </c>
       <c r="AO11" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO11, LEN('Éves adatsor'!AO11) - 3)</f>
@@ -10869,9 +10899,9 @@
         <f>LEFT('Éves adatsor'!AM12, LEN('Éves adatsor'!AM12) - 3)</f>
         <v>10</v>
       </c>
-      <c r="AN12" s="14" t="e">
+      <c r="AN12" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN12, LEN('Éves adatsor'!AN12) - 3)</f>
-        <v>#VALUE!</v>
+        <v>9</v>
       </c>
       <c r="AO12" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO12, LEN('Éves adatsor'!AO12) - 3)</f>
@@ -11046,9 +11076,9 @@
         <f>LEFT('Éves adatsor'!AM13, LEN('Éves adatsor'!AM13) - 3)</f>
         <v>9</v>
       </c>
-      <c r="AN13" s="14" t="e">
+      <c r="AN13" s="14" t="str">
         <f>LEFT('Éves adatsor'!AN13, LEN('Éves adatsor'!AN13) - 3)</f>
-        <v>#VALUE!</v>
+        <v>9</v>
       </c>
       <c r="AO13" s="14" t="e">
         <f>LEFT('Éves adatsor'!AO13, LEN('Éves adatsor'!AO13) - 3)</f>
@@ -11558,9 +11588,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="11" t="e">
+      <c r="AN19" s="11">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="11" t="e">
         <f t="shared" si="5"/>
@@ -12074,9 +12104,9 @@
         <f t="shared" si="11"/>
         <v>-0.1111111111111111</v>
       </c>
-      <c r="AN22" s="11" t="e">
+      <c r="AN22" s="11">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="AO22" s="11" t="e">
         <f t="shared" si="11"/>
@@ -12246,9 +12276,9 @@
         <f t="shared" si="13"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AN23" s="11" t="e">
+      <c r="AN23" s="11">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AO23" s="11" t="e">
         <f t="shared" si="13"/>
@@ -12418,9 +12448,9 @@
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AN24" s="11" t="e">
+      <c r="AN24" s="11">
         <f t="shared" si="15"/>
-        <v>#VALUE!</v>
+        <v>0.25</v>
       </c>
       <c r="AO24" s="11" t="e">
         <f t="shared" si="15"/>
